--- a/template/스마트 견적서.xlsx
+++ b/template/스마트 견적서.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21690" windowHeight="10470" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21690" windowHeight="10470"/>
   </bookViews>
   <sheets>
     <sheet name="1)내역집계표" sheetId="3" r:id="rId1"/>
@@ -831,7 +831,7 @@
     <definedName name="PPP" hidden="1">{#N/A,#N/A,FALSE,"CCTV"}</definedName>
     <definedName name="PQR" hidden="1">{#N/A,#N/A,FALSE,"TABLE"}</definedName>
     <definedName name="PRAYER" hidden="1">{#N/A,#N/A,FALSE,"CCTV"}</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'1)내역집계표'!$A$1:$J$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'1)내역집계표'!$A$1:$H$34</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'2)상세내역서'!$A$1:$H$9</definedName>
     <definedName name="q" hidden="1">{#N/A,#N/A,FALSE,"현장 NCR 분석";#N/A,#N/A,FALSE,"현장품질감사";#N/A,#N/A,FALSE,"현장품질감사"}</definedName>
     <definedName name="q00" hidden="1">{#N/A,#N/A,FALSE,"운반시간"}</definedName>
@@ -9676,7 +9676,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -9743,9 +9743,6 @@
     <xf numFmtId="41" fontId="17" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="17" fillId="0" borderId="2" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="177" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -9863,36 +9860,42 @@
     <xf numFmtId="177" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="15" fillId="3" borderId="19" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="17" fillId="2" borderId="2" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="17" fillId="0" borderId="2" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -9913,12 +9916,6 @@
     </xf>
     <xf numFmtId="177" fontId="15" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="118" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="118" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2769">
@@ -12714,13 +12711,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>122464</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>124071</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>3374570</xdr:colOff>
       <xdr:row>9</xdr:row>
       <xdr:rowOff>195305</xdr:rowOff>
@@ -12738,7 +12735,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="10940143" y="3729964"/>
+          <a:off x="11810199" y="3732365"/>
           <a:ext cx="3252106" cy="452234"/>
           <a:chOff x="7814441" y="1341884"/>
           <a:chExt cx="4333615" cy="469308"/>
@@ -12819,7 +12816,7 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>2089041</xdr:colOff>
       <xdr:row>11</xdr:row>
       <xdr:rowOff>252793</xdr:rowOff>
@@ -12889,15 +12886,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>164086</xdr:colOff>
+      <xdr:colOff>78439</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>48825</xdr:rowOff>
+      <xdr:rowOff>71236</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>3346556</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>3910853</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>272943</xdr:rowOff>
+      <xdr:rowOff>295354</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -12912,8 +12909,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="164086" y="987718"/>
-          <a:ext cx="14163434" cy="2510118"/>
+          <a:off x="78439" y="1012530"/>
+          <a:ext cx="15520149" cy="2510118"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -14237,563 +14234,493 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K91"/>
+  <dimension ref="A1:I91"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.85546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="22.85546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="37.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19" style="1" customWidth="1"/>
-    <col min="6" max="7" width="9.85546875" style="1" customWidth="1"/>
-    <col min="8" max="9" width="22.85546875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="52.42578125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="12.42578125" style="49" customWidth="1"/>
-    <col min="12" max="141" width="11.42578125" style="1"/>
-    <col min="142" max="149" width="11.42578125" style="1" customWidth="1"/>
-    <col min="150" max="16384" width="11.42578125" style="1"/>
+    <col min="2" max="2" width="83.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19" style="1" customWidth="1"/>
+    <col min="4" max="5" width="9.85546875" style="1" customWidth="1"/>
+    <col min="6" max="7" width="22.85546875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="60" style="1" customWidth="1"/>
+    <col min="9" max="9" width="12.42578125" style="48" customWidth="1"/>
+    <col min="10" max="139" width="11.42578125" style="1"/>
+    <col min="140" max="147" width="11.42578125" style="1" customWidth="1"/>
+    <col min="148" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="74.25" customHeight="1">
-      <c r="A1" s="62" t="s">
+    <row r="1" spans="1:9" ht="74.25" customHeight="1">
+      <c r="A1" s="72" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="46"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
+      <c r="I1" s="45"/>
     </row>
-    <row r="2" spans="1:11" ht="30" customHeight="1">
-      <c r="A2" s="26"/>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="K2" s="46"/>
+    <row r="2" spans="1:9" ht="30" customHeight="1">
+      <c r="A2" s="25"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="I2" s="45"/>
     </row>
-    <row r="3" spans="1:11" ht="30" customHeight="1">
-      <c r="A3" s="26"/>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
-      <c r="K3" s="46"/>
+    <row r="3" spans="1:9" ht="30" customHeight="1">
+      <c r="A3" s="25"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="25"/>
+      <c r="I3" s="45"/>
     </row>
-    <row r="4" spans="1:11" ht="30" customHeight="1">
-      <c r="A4" s="26"/>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
-      <c r="K4" s="46"/>
+    <row r="4" spans="1:9" ht="30" customHeight="1">
+      <c r="A4" s="25"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="I4" s="45"/>
     </row>
-    <row r="5" spans="1:11" ht="30" customHeight="1">
-      <c r="A5" s="26"/>
-      <c r="B5" s="26"/>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26"/>
-      <c r="I5" s="26"/>
-      <c r="K5" s="46"/>
+    <row r="5" spans="1:9" ht="30" customHeight="1">
+      <c r="A5" s="25"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
+      <c r="I5" s="45"/>
     </row>
-    <row r="6" spans="1:11" ht="30" customHeight="1">
-      <c r="A6" s="26"/>
-      <c r="B6" s="26"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="26"/>
-      <c r="I6" s="26"/>
-      <c r="K6" s="46"/>
+    <row r="6" spans="1:9" ht="30" customHeight="1">
+      <c r="A6" s="25"/>
+      <c r="B6" s="25"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="25"/>
+      <c r="I6" s="45"/>
     </row>
-    <row r="7" spans="1:11" ht="30" customHeight="1">
-      <c r="A7" s="26"/>
-      <c r="B7" s="26"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
-      <c r="F7" s="26"/>
-      <c r="G7" s="26"/>
-      <c r="H7" s="26"/>
-      <c r="I7" s="26"/>
-      <c r="K7" s="46"/>
+    <row r="7" spans="1:9" ht="30" customHeight="1">
+      <c r="A7" s="25"/>
+      <c r="B7" s="25"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25"/>
+      <c r="I7" s="45"/>
     </row>
-    <row r="8" spans="1:11" ht="30" customHeight="1">
-      <c r="A8" s="26"/>
-      <c r="B8" s="26"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="26"/>
-      <c r="I8" s="26"/>
-      <c r="K8" s="46"/>
+    <row r="8" spans="1:9" ht="30" customHeight="1">
+      <c r="A8" s="25"/>
+      <c r="B8" s="25"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
+      <c r="I8" s="45"/>
     </row>
-    <row r="9" spans="1:11" ht="30" customHeight="1">
-      <c r="A9" s="31" t="s">
+    <row r="9" spans="1:9" ht="30" customHeight="1">
+      <c r="A9" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="B9" s="28"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="28"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="28"/>
-      <c r="I9" s="28"/>
-      <c r="K9" s="46"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="27"/>
+      <c r="I9" s="45"/>
     </row>
-    <row r="10" spans="1:11" ht="30" customHeight="1">
-      <c r="A10" s="31" t="s">
+    <row r="10" spans="1:9" ht="30" customHeight="1">
+      <c r="A10" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="B10" s="28"/>
-      <c r="C10" s="28"/>
-      <c r="D10" s="28"/>
-      <c r="E10" s="28"/>
-      <c r="F10" s="28"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="28"/>
-      <c r="I10" s="28"/>
-      <c r="K10" s="46"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="27"/>
+      <c r="I10" s="45"/>
     </row>
-    <row r="11" spans="1:11" ht="30" customHeight="1">
-      <c r="A11" s="31" t="s">
+    <row r="11" spans="1:9" ht="30" customHeight="1">
+      <c r="A11" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="B11" s="28"/>
-      <c r="C11" s="28"/>
-      <c r="D11" s="28"/>
-      <c r="E11" s="28"/>
-      <c r="F11" s="28"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
       <c r="G11" s="28"/>
-      <c r="I11" s="29"/>
-      <c r="J11" s="58" t="s">
+      <c r="H11" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="K11" s="46"/>
+      <c r="I11" s="45"/>
     </row>
-    <row r="12" spans="1:11" ht="30" customHeight="1">
-      <c r="A12" s="31" t="s">
+    <row r="12" spans="1:9" ht="30" customHeight="1">
+      <c r="A12" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="28"/>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27"/>
       <c r="G12" s="28"/>
-      <c r="I12" s="29"/>
-      <c r="J12" s="58" t="s">
+      <c r="H12" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="K12" s="46"/>
+      <c r="I12" s="45"/>
     </row>
-    <row r="13" spans="1:11" ht="30" customHeight="1">
-      <c r="A13" s="31" t="s">
+    <row r="13" spans="1:9" ht="30" customHeight="1">
+      <c r="A13" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="28"/>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
+      <c r="B13" s="27"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
       <c r="G13" s="28"/>
-      <c r="I13" s="29"/>
-      <c r="J13" s="58" t="s">
+      <c r="H13" s="57" t="s">
         <v>24</v>
       </c>
-      <c r="K13" s="46"/>
+      <c r="I13" s="45"/>
     </row>
-    <row r="14" spans="1:11" ht="30" customHeight="1">
-      <c r="A14" s="31" t="s">
+    <row r="14" spans="1:9" ht="30" customHeight="1">
+      <c r="A14" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="B14" s="28"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="28"/>
+      <c r="B14" s="27"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
       <c r="G14" s="28"/>
-      <c r="I14" s="29"/>
-      <c r="J14" s="58" t="s">
+      <c r="H14" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="K14" s="46"/>
+      <c r="I14" s="45"/>
     </row>
-    <row r="15" spans="1:11" ht="30" customHeight="1">
-      <c r="A15" s="31" t="s">
+    <row r="15" spans="1:9" ht="30" customHeight="1">
+      <c r="A15" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="B15" s="28"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
+      <c r="B15" s="27"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
       <c r="G15" s="28"/>
-      <c r="I15" s="29"/>
-      <c r="J15" s="59" t="s">
+      <c r="H15" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="K15" s="46"/>
+      <c r="I15" s="45"/>
     </row>
-    <row r="16" spans="1:11" ht="30" customHeight="1">
-      <c r="A16" s="27"/>
-      <c r="B16" s="30"/>
-      <c r="C16" s="60"/>
-      <c r="D16" s="60"/>
-      <c r="E16" s="60"/>
-      <c r="F16" s="60"/>
-      <c r="G16" s="60"/>
-      <c r="H16" s="60"/>
-      <c r="I16" s="60"/>
-      <c r="J16" s="32" t="s">
+    <row r="16" spans="1:9" ht="30" customHeight="1">
+      <c r="A16" s="26"/>
+      <c r="B16" s="29"/>
+      <c r="C16" s="59"/>
+      <c r="D16" s="59"/>
+      <c r="E16" s="59"/>
+      <c r="F16" s="59"/>
+      <c r="G16" s="59"/>
+      <c r="H16" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="K16" s="46"/>
+      <c r="I16" s="45"/>
     </row>
-    <row r="17" spans="1:11" s="3" customFormat="1" ht="30" customHeight="1">
+    <row r="17" spans="1:9" s="3" customFormat="1" ht="30" customHeight="1">
       <c r="A17" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B17" s="63" t="s">
+      <c r="B17" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="C17" s="64"/>
-      <c r="D17" s="65"/>
-      <c r="E17" s="2" t="s">
+      <c r="C17" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="D17" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="E17" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H17" s="2" t="s">
+      <c r="F17" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I17" s="2" t="s">
+      <c r="G17" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J17" s="2" t="s">
+      <c r="H17" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K17" s="47" t="s">
+      <c r="I17" s="46" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="18" spans="1:11" s="8" customFormat="1" ht="30" customHeight="1">
+    <row r="18" spans="1:9" s="8" customFormat="1" ht="30" customHeight="1">
       <c r="A18" s="4">
         <v>1</v>
       </c>
-      <c r="B18" s="66" t="s">
+      <c r="B18" s="65" t="s">
         <v>56</v>
       </c>
-      <c r="C18" s="67"/>
-      <c r="D18" s="68"/>
-      <c r="E18" s="5" t="s">
+      <c r="C18" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="D18" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G18" s="6"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="5"/>
-      <c r="K18" s="61" t="s">
+      <c r="E18" s="6"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="60" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="19" spans="1:11" s="8" customFormat="1" ht="30" customHeight="1">
+    <row r="19" spans="1:9" s="8" customFormat="1" ht="30" customHeight="1">
       <c r="A19" s="9"/>
-      <c r="B19" s="69" t="s">
+      <c r="B19" s="66" t="s">
         <v>57</v>
       </c>
-      <c r="C19" s="70"/>
-      <c r="D19" s="71"/>
-      <c r="E19" s="10" t="s">
+      <c r="C19" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F19" s="10" t="s">
+      <c r="D19" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G19" s="11"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="10"/>
-      <c r="K19" s="61" t="s">
+      <c r="E19" s="11"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="60" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="20" spans="1:11" s="8" customFormat="1" ht="30" customHeight="1">
+    <row r="20" spans="1:9" s="8" customFormat="1" ht="30" customHeight="1">
       <c r="A20" s="9"/>
-      <c r="B20" s="69"/>
-      <c r="C20" s="70"/>
-      <c r="D20" s="71"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="12"/>
-      <c r="J20" s="10"/>
-      <c r="K20" s="47" t="s">
+      <c r="B20" s="62"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="46" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="35.1" customHeight="1">
-      <c r="A21" s="74" t="s">
+    <row r="21" spans="1:9" ht="35.1" customHeight="1">
+      <c r="A21" s="75" t="s">
         <v>58</v>
       </c>
-      <c r="B21" s="74"/>
-      <c r="C21" s="74"/>
-      <c r="D21" s="74"/>
-      <c r="E21" s="74"/>
-      <c r="F21" s="74"/>
-      <c r="G21" s="74"/>
-      <c r="H21" s="54"/>
-      <c r="I21" s="55"/>
-      <c r="J21" s="13" t="s">
+      <c r="B21" s="75"/>
+      <c r="C21" s="75"/>
+      <c r="D21" s="75"/>
+      <c r="E21" s="75"/>
+      <c r="F21" s="53"/>
+      <c r="G21" s="54"/>
+      <c r="H21" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="K21" s="47" t="s">
+      <c r="I21" s="46" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="22" spans="1:11" s="38" customFormat="1" ht="30" customHeight="1">
-      <c r="A22" s="72" t="s">
+    <row r="22" spans="1:9" s="37" customFormat="1" ht="30" customHeight="1">
+      <c r="A22" s="73" t="s">
         <v>28</v>
       </c>
-      <c r="B22" s="73"/>
-      <c r="C22" s="73"/>
-      <c r="D22" s="73"/>
-      <c r="E22" s="73"/>
-      <c r="F22" s="73"/>
-      <c r="G22" s="73"/>
-      <c r="H22" s="73"/>
-      <c r="I22" s="73"/>
-      <c r="J22" s="50"/>
-      <c r="K22" s="47"/>
+      <c r="B22" s="74"/>
+      <c r="C22" s="74"/>
+      <c r="D22" s="74"/>
+      <c r="E22" s="74"/>
+      <c r="F22" s="74"/>
+      <c r="G22" s="74"/>
+      <c r="H22" s="49"/>
+      <c r="I22" s="46"/>
     </row>
-    <row r="23" spans="1:11" s="39" customFormat="1" ht="30" customHeight="1">
-      <c r="A23" s="72" t="s">
+    <row r="23" spans="1:9" s="38" customFormat="1" ht="30" customHeight="1">
+      <c r="A23" s="73" t="s">
         <v>29</v>
       </c>
-      <c r="B23" s="73"/>
-      <c r="C23" s="73"/>
-      <c r="D23" s="73"/>
-      <c r="E23" s="73"/>
-      <c r="F23" s="73"/>
-      <c r="G23" s="73"/>
-      <c r="H23" s="73"/>
-      <c r="I23" s="73"/>
-      <c r="J23" s="50"/>
-      <c r="K23" s="47"/>
+      <c r="B23" s="74"/>
+      <c r="C23" s="74"/>
+      <c r="D23" s="74"/>
+      <c r="E23" s="74"/>
+      <c r="F23" s="74"/>
+      <c r="G23" s="74"/>
+      <c r="H23" s="49"/>
+      <c r="I23" s="46"/>
     </row>
-    <row r="24" spans="1:11" s="39" customFormat="1" ht="30" customHeight="1">
-      <c r="A24" s="72" t="s">
+    <row r="24" spans="1:9" s="38" customFormat="1" ht="30" customHeight="1">
+      <c r="A24" s="73" t="s">
         <v>30</v>
       </c>
-      <c r="B24" s="73"/>
-      <c r="C24" s="73"/>
-      <c r="D24" s="73"/>
-      <c r="E24" s="73"/>
-      <c r="F24" s="73"/>
-      <c r="G24" s="73"/>
-      <c r="H24" s="73"/>
-      <c r="I24" s="73"/>
-      <c r="J24" s="50"/>
-      <c r="K24" s="47"/>
+      <c r="B24" s="74"/>
+      <c r="C24" s="74"/>
+      <c r="D24" s="74"/>
+      <c r="E24" s="74"/>
+      <c r="F24" s="74"/>
+      <c r="G24" s="74"/>
+      <c r="H24" s="49"/>
+      <c r="I24" s="46"/>
     </row>
-    <row r="25" spans="1:11" s="39" customFormat="1" ht="30" customHeight="1">
-      <c r="A25" s="72" t="s">
+    <row r="25" spans="1:9" s="38" customFormat="1" ht="30" customHeight="1">
+      <c r="A25" s="73" t="s">
         <v>31</v>
       </c>
-      <c r="B25" s="73"/>
-      <c r="C25" s="73"/>
-      <c r="D25" s="73"/>
-      <c r="E25" s="73"/>
-      <c r="F25" s="73"/>
-      <c r="G25" s="73"/>
-      <c r="H25" s="73"/>
-      <c r="I25" s="73"/>
-      <c r="J25" s="50"/>
-      <c r="K25" s="47"/>
+      <c r="B25" s="74"/>
+      <c r="C25" s="74"/>
+      <c r="D25" s="74"/>
+      <c r="E25" s="74"/>
+      <c r="F25" s="74"/>
+      <c r="G25" s="74"/>
+      <c r="H25" s="49"/>
+      <c r="I25" s="46"/>
     </row>
-    <row r="26" spans="1:11" s="39" customFormat="1" ht="30" customHeight="1">
-      <c r="A26" s="72" t="s">
+    <row r="26" spans="1:9" s="38" customFormat="1" ht="30" customHeight="1">
+      <c r="A26" s="73" t="s">
         <v>40</v>
       </c>
-      <c r="B26" s="73"/>
-      <c r="C26" s="73"/>
-      <c r="D26" s="73"/>
-      <c r="E26" s="73"/>
-      <c r="F26" s="73"/>
-      <c r="G26" s="73"/>
-      <c r="H26" s="73"/>
-      <c r="I26" s="73"/>
-      <c r="J26" s="50"/>
-      <c r="K26" s="47"/>
+      <c r="B26" s="74"/>
+      <c r="C26" s="74"/>
+      <c r="D26" s="74"/>
+      <c r="E26" s="74"/>
+      <c r="F26" s="74"/>
+      <c r="G26" s="74"/>
+      <c r="H26" s="49"/>
+      <c r="I26" s="46"/>
     </row>
-    <row r="27" spans="1:11" s="39" customFormat="1" ht="30" customHeight="1">
-      <c r="A27" s="72" t="s">
+    <row r="27" spans="1:9" s="38" customFormat="1" ht="30" customHeight="1">
+      <c r="A27" s="73" t="s">
         <v>32</v>
       </c>
-      <c r="B27" s="73"/>
-      <c r="C27" s="73"/>
-      <c r="D27" s="73"/>
-      <c r="E27" s="73"/>
-      <c r="F27" s="73"/>
-      <c r="G27" s="73"/>
-      <c r="H27" s="73"/>
-      <c r="I27" s="73"/>
-      <c r="J27" s="50"/>
-      <c r="K27" s="47"/>
+      <c r="B27" s="74"/>
+      <c r="C27" s="74"/>
+      <c r="D27" s="74"/>
+      <c r="E27" s="74"/>
+      <c r="F27" s="74"/>
+      <c r="G27" s="74"/>
+      <c r="H27" s="49"/>
+      <c r="I27" s="46"/>
     </row>
-    <row r="28" spans="1:11" s="39" customFormat="1" ht="30" customHeight="1">
-      <c r="A28" s="72" t="s">
+    <row r="28" spans="1:9" s="38" customFormat="1" ht="30" customHeight="1">
+      <c r="A28" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="B28" s="73"/>
-      <c r="C28" s="73"/>
-      <c r="D28" s="73"/>
-      <c r="E28" s="73"/>
-      <c r="F28" s="73"/>
-      <c r="G28" s="73"/>
-      <c r="H28" s="73"/>
-      <c r="I28" s="73"/>
-      <c r="J28" s="50"/>
-      <c r="K28" s="47"/>
+      <c r="B28" s="74"/>
+      <c r="C28" s="74"/>
+      <c r="D28" s="74"/>
+      <c r="E28" s="74"/>
+      <c r="F28" s="74"/>
+      <c r="G28" s="74"/>
+      <c r="H28" s="49"/>
+      <c r="I28" s="46"/>
     </row>
-    <row r="29" spans="1:11" s="39" customFormat="1" ht="30" customHeight="1">
-      <c r="A29" s="72" t="s">
+    <row r="29" spans="1:9" s="38" customFormat="1" ht="30" customHeight="1">
+      <c r="A29" s="73" t="s">
         <v>34</v>
       </c>
-      <c r="B29" s="73"/>
-      <c r="C29" s="73"/>
-      <c r="D29" s="73"/>
-      <c r="E29" s="73"/>
-      <c r="F29" s="73"/>
-      <c r="G29" s="73"/>
-      <c r="H29" s="73"/>
-      <c r="I29" s="73"/>
-      <c r="J29" s="50"/>
-      <c r="K29" s="47"/>
+      <c r="B29" s="74"/>
+      <c r="C29" s="74"/>
+      <c r="D29" s="74"/>
+      <c r="E29" s="74"/>
+      <c r="F29" s="74"/>
+      <c r="G29" s="74"/>
+      <c r="H29" s="49"/>
+      <c r="I29" s="46"/>
     </row>
-    <row r="30" spans="1:11" s="39" customFormat="1" ht="30" customHeight="1">
-      <c r="A30" s="72" t="s">
+    <row r="30" spans="1:9" s="38" customFormat="1" ht="30" customHeight="1">
+      <c r="A30" s="73" t="s">
         <v>35</v>
       </c>
-      <c r="B30" s="73"/>
-      <c r="C30" s="73"/>
-      <c r="D30" s="73"/>
-      <c r="E30" s="73"/>
-      <c r="F30" s="73"/>
-      <c r="G30" s="73"/>
-      <c r="H30" s="73"/>
-      <c r="I30" s="73"/>
-      <c r="J30" s="50"/>
-      <c r="K30" s="47"/>
+      <c r="B30" s="74"/>
+      <c r="C30" s="74"/>
+      <c r="D30" s="74"/>
+      <c r="E30" s="74"/>
+      <c r="F30" s="74"/>
+      <c r="G30" s="74"/>
+      <c r="H30" s="49"/>
+      <c r="I30" s="46"/>
     </row>
-    <row r="31" spans="1:11" s="39" customFormat="1" ht="30" customHeight="1">
-      <c r="A31" s="72" t="s">
+    <row r="31" spans="1:9" s="38" customFormat="1" ht="30" customHeight="1">
+      <c r="A31" s="73" t="s">
         <v>36</v>
       </c>
-      <c r="B31" s="73"/>
-      <c r="C31" s="73"/>
-      <c r="D31" s="73"/>
-      <c r="E31" s="73"/>
-      <c r="F31" s="73"/>
-      <c r="G31" s="73"/>
-      <c r="H31" s="73"/>
-      <c r="I31" s="73"/>
-      <c r="J31" s="50"/>
-      <c r="K31" s="47"/>
+      <c r="B31" s="74"/>
+      <c r="C31" s="74"/>
+      <c r="D31" s="74"/>
+      <c r="E31" s="74"/>
+      <c r="F31" s="74"/>
+      <c r="G31" s="74"/>
+      <c r="H31" s="49"/>
+      <c r="I31" s="46"/>
     </row>
-    <row r="32" spans="1:11" s="39" customFormat="1" ht="30" customHeight="1">
-      <c r="A32" s="72" t="s">
+    <row r="32" spans="1:9" s="38" customFormat="1" ht="30" customHeight="1">
+      <c r="A32" s="73" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="73"/>
-      <c r="C32" s="73"/>
-      <c r="D32" s="73"/>
-      <c r="E32" s="73"/>
-      <c r="F32" s="73"/>
-      <c r="G32" s="73"/>
-      <c r="H32" s="73"/>
-      <c r="I32" s="73"/>
-      <c r="J32" s="50"/>
-      <c r="K32" s="47"/>
+      <c r="B32" s="74"/>
+      <c r="C32" s="74"/>
+      <c r="D32" s="74"/>
+      <c r="E32" s="74"/>
+      <c r="F32" s="74"/>
+      <c r="G32" s="74"/>
+      <c r="H32" s="49"/>
+      <c r="I32" s="46"/>
     </row>
-    <row r="33" spans="1:11" s="39" customFormat="1" ht="30" customHeight="1">
-      <c r="A33" s="72" t="s">
+    <row r="33" spans="1:9" s="38" customFormat="1" ht="30" customHeight="1">
+      <c r="A33" s="73" t="s">
         <v>41</v>
       </c>
-      <c r="B33" s="73"/>
-      <c r="C33" s="73"/>
-      <c r="D33" s="73"/>
-      <c r="E33" s="73"/>
-      <c r="F33" s="73"/>
-      <c r="G33" s="73"/>
-      <c r="H33" s="73"/>
-      <c r="I33" s="73"/>
-      <c r="J33" s="50"/>
-      <c r="K33" s="47"/>
+      <c r="B33" s="74"/>
+      <c r="C33" s="74"/>
+      <c r="D33" s="74"/>
+      <c r="E33" s="74"/>
+      <c r="F33" s="74"/>
+      <c r="G33" s="74"/>
+      <c r="H33" s="49"/>
+      <c r="I33" s="46"/>
     </row>
-    <row r="34" spans="1:11" s="39" customFormat="1" ht="30" customHeight="1">
-      <c r="A34" s="72" t="s">
+    <row r="34" spans="1:9" s="38" customFormat="1" ht="30" customHeight="1">
+      <c r="A34" s="73" t="s">
         <v>38</v>
       </c>
-      <c r="B34" s="73"/>
-      <c r="C34" s="73"/>
-      <c r="D34" s="73"/>
-      <c r="E34" s="73"/>
-      <c r="F34" s="73"/>
-      <c r="G34" s="73"/>
-      <c r="H34" s="73"/>
-      <c r="I34" s="73"/>
-      <c r="J34" s="51"/>
-      <c r="K34" s="47"/>
+      <c r="B34" s="74"/>
+      <c r="C34" s="74"/>
+      <c r="D34" s="74"/>
+      <c r="E34" s="74"/>
+      <c r="F34" s="74"/>
+      <c r="G34" s="74"/>
+      <c r="H34" s="50"/>
+      <c r="I34" s="46"/>
     </row>
-    <row r="35" spans="1:11" ht="24.95" customHeight="1"/>
-    <row r="36" spans="1:11" ht="24.95" customHeight="1"/>
-    <row r="37" spans="1:11" ht="24.95" customHeight="1"/>
-    <row r="38" spans="1:11" ht="24.95" customHeight="1"/>
-    <row r="39" spans="1:11" ht="24.95" customHeight="1"/>
-    <row r="40" spans="1:11" ht="24.95" customHeight="1"/>
-    <row r="41" spans="1:11" ht="24.95" customHeight="1"/>
-    <row r="42" spans="1:11" ht="24.95" customHeight="1"/>
-    <row r="43" spans="1:11" ht="24.95" customHeight="1"/>
-    <row r="44" spans="1:11" ht="24.95" customHeight="1"/>
-    <row r="45" spans="1:11" ht="24.95" customHeight="1"/>
-    <row r="46" spans="1:11" ht="24.95" customHeight="1"/>
-    <row r="47" spans="1:11" ht="24.95" customHeight="1"/>
-    <row r="48" spans="1:11" ht="24.95" customHeight="1"/>
+    <row r="35" spans="1:9" ht="24.95" customHeight="1"/>
+    <row r="36" spans="1:9" ht="24.95" customHeight="1"/>
+    <row r="37" spans="1:9" ht="24.95" customHeight="1"/>
+    <row r="38" spans="1:9" ht="24.95" customHeight="1"/>
+    <row r="39" spans="1:9" ht="24.95" customHeight="1"/>
+    <row r="40" spans="1:9" ht="24.95" customHeight="1"/>
+    <row r="41" spans="1:9" ht="24.95" customHeight="1"/>
+    <row r="42" spans="1:9" ht="24.95" customHeight="1"/>
+    <row r="43" spans="1:9" ht="24.95" customHeight="1"/>
+    <row r="44" spans="1:9" ht="24.95" customHeight="1"/>
+    <row r="45" spans="1:9" ht="24.95" customHeight="1"/>
+    <row r="46" spans="1:9" ht="24.95" customHeight="1"/>
+    <row r="47" spans="1:9" ht="24.95" customHeight="1"/>
+    <row r="48" spans="1:9" ht="24.95" customHeight="1"/>
     <row r="49" ht="24.95" customHeight="1"/>
     <row r="50" ht="24.95" customHeight="1"/>
     <row r="51" ht="24.95" customHeight="1"/>
@@ -14838,34 +14765,30 @@
     <row r="90" ht="24.95" customHeight="1"/>
     <row r="91" ht="24.95" customHeight="1"/>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="A32:I32"/>
-    <mergeCell ref="A33:I33"/>
-    <mergeCell ref="A34:I34"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="A26:I26"/>
-    <mergeCell ref="A27:I27"/>
-    <mergeCell ref="A28:I28"/>
-    <mergeCell ref="A29:I29"/>
-    <mergeCell ref="A30:I30"/>
-    <mergeCell ref="A22:I22"/>
-    <mergeCell ref="A23:I23"/>
-    <mergeCell ref="A24:I24"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A25:I25"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A31:I31"/>
+  <mergeCells count="15">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A25:G25"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="J15" r:id="rId1"/>
+    <hyperlink ref="H15" r:id="rId1"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.39370078740157483" bottom="0.31496062992125984" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="46" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" scale="42" orientation="portrait" r:id="rId2"/>
   <drawing r:id="rId3"/>
 </worksheet>
 </file>
@@ -14878,150 +14801,150 @@
   <dimension ref="A1:I9"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="5.85546875" style="23" customWidth="1"/>
-    <col min="2" max="2" width="43.85546875" style="35" customWidth="1"/>
-    <col min="3" max="3" width="128.140625" style="37" customWidth="1"/>
-    <col min="4" max="4" width="8.7109375" style="23" customWidth="1"/>
-    <col min="5" max="5" width="8.7109375" style="24" customWidth="1"/>
+    <col min="1" max="1" width="5.85546875" style="22" customWidth="1"/>
+    <col min="2" max="2" width="43.85546875" style="34" customWidth="1"/>
+    <col min="3" max="3" width="128.140625" style="36" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" style="22" customWidth="1"/>
+    <col min="5" max="5" width="8.7109375" style="23" customWidth="1"/>
     <col min="6" max="7" width="20.28515625" style="14" customWidth="1"/>
-    <col min="8" max="8" width="18.85546875" style="25" customWidth="1"/>
+    <col min="8" max="8" width="18.85546875" style="24" customWidth="1"/>
     <col min="9" max="16384" width="11.42578125" style="14"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="54.95" customHeight="1">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
-      <c r="H1" s="76"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
     </row>
     <row r="2" spans="1:9" s="15" customFormat="1" ht="24.95" customHeight="1">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
       <c r="I2" s="16"/>
     </row>
     <row r="3" spans="1:9" s="15" customFormat="1" ht="24.95" customHeight="1">
-      <c r="A3" s="44" t="s">
+      <c r="A3" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="44"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="33" t="s">
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="32" t="s">
         <v>27</v>
       </c>
       <c r="I3" s="16"/>
     </row>
     <row r="4" spans="1:9" s="16" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A4" s="75" t="s">
+      <c r="A4" s="76" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="77" t="s">
+      <c r="B4" s="78" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="77" t="s">
+      <c r="C4" s="78" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="78" t="s">
+      <c r="D4" s="79" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="78" t="s">
+      <c r="E4" s="79" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="78"/>
-      <c r="G4" s="78"/>
-      <c r="H4" s="75" t="s">
+      <c r="F4" s="79"/>
+      <c r="G4" s="79"/>
+      <c r="H4" s="76" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="16" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A5" s="75"/>
-      <c r="B5" s="77"/>
-      <c r="C5" s="77"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="43" t="s">
+      <c r="A5" s="76"/>
+      <c r="B5" s="78"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="42" t="s">
+      <c r="F5" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="42" t="s">
+      <c r="G5" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="75"/>
-      <c r="I5" s="79" t="s">
+      <c r="H5" s="76"/>
+      <c r="I5" s="63" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="1:9" s="48" customFormat="1" ht="24.95" customHeight="1">
-      <c r="A6" s="56"/>
-      <c r="B6" s="45" t="s">
+    <row r="6" spans="1:9" s="47" customFormat="1" ht="24.95" customHeight="1">
+      <c r="A6" s="55"/>
+      <c r="B6" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="80" t="s">
+      <c r="C6" s="44"/>
+      <c r="D6" s="55"/>
+      <c r="E6" s="55"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="67"/>
+      <c r="H6" s="55"/>
+      <c r="I6" s="64" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="7" spans="1:9" s="48" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A7" s="57"/>
-      <c r="B7" s="36" t="s">
+    <row r="7" spans="1:9" s="47" customFormat="1" ht="24.75" customHeight="1">
+      <c r="A7" s="56"/>
+      <c r="B7" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="C7" s="36"/>
-      <c r="D7" s="36"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="36"/>
-      <c r="G7" s="36"/>
-      <c r="H7" s="36"/>
-      <c r="I7" s="48" t="s">
+      <c r="C7" s="35"/>
+      <c r="D7" s="56"/>
+      <c r="E7" s="56"/>
+      <c r="F7" s="69"/>
+      <c r="G7" s="68"/>
+      <c r="H7" s="56"/>
+      <c r="I7" s="47" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="24.75" customHeight="1">
       <c r="A8" s="17"/>
-      <c r="B8" s="34"/>
-      <c r="C8" s="53"/>
+      <c r="B8" s="33"/>
+      <c r="C8" s="52"/>
       <c r="D8" s="18"/>
       <c r="E8" s="19"/>
       <c r="F8" s="20"/>
       <c r="G8" s="21"/>
-      <c r="H8" s="22"/>
+      <c r="H8" s="71"/>
       <c r="I8" s="14" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="24.95" customHeight="1">
       <c r="A9" s="17"/>
-      <c r="B9" s="41"/>
-      <c r="C9" s="52"/>
+      <c r="B9" s="40"/>
+      <c r="C9" s="51"/>
       <c r="D9" s="18"/>
       <c r="E9" s="19"/>
       <c r="F9" s="20"/>
       <c r="G9" s="21"/>
-      <c r="H9" s="22"/>
-      <c r="I9" s="79" t="s">
+      <c r="H9" s="71"/>
+      <c r="I9" s="63" t="s">
         <v>59</v>
       </c>
     </row>
